--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,6 +845,34 @@
         <v>523.35</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026年2月13日</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>123.14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>123.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -861,7 +861,7 @@
         <v>123.14</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>171.49</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>123.14</v>
+        <v>294.63</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -864,13 +864,13 @@
         <v>171.49</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>129.34</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>106.05</v>
       </c>
       <c r="H16" t="n">
-        <v>294.63</v>
+        <v>530.02</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -478,7 +478,7 @@
         <v>103.33</v>
       </c>
       <c r="H2" t="n">
-        <v>485.862</v>
+        <v>485.86</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +506,7 @@
         <v>103.82</v>
       </c>
       <c r="H3" t="n">
-        <v>488.8899999999999</v>
+        <v>488.89</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>103.54</v>
       </c>
       <c r="H5" t="n">
-        <v>482.0277</v>
+        <v>482.03</v>
       </c>
     </row>
     <row r="6">
@@ -590,7 +590,7 @@
         <v>103.54</v>
       </c>
       <c r="H6" t="n">
-        <v>482.8986</v>
+        <v>482.9</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         <v>103.66</v>
       </c>
       <c r="H7" t="n">
-        <v>479.978</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>103.85</v>
       </c>
       <c r="H8" t="n">
-        <v>481.4449999999999</v>
+        <v>481.44</v>
       </c>
     </row>
     <row r="9">
@@ -674,7 +674,7 @@
         <v>104.39</v>
       </c>
       <c r="H9" t="n">
-        <v>496.3589999999999</v>
+        <v>496.36</v>
       </c>
     </row>
     <row r="10">
@@ -702,7 +702,7 @@
         <v>104.05</v>
       </c>
       <c r="H10" t="n">
-        <v>494.2348</v>
+        <v>494.23</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>104.31</v>
       </c>
       <c r="H11" t="n">
-        <v>515.415</v>
+        <v>515.42</v>
       </c>
     </row>
     <row r="12">
@@ -758,7 +758,7 @@
         <v>105.12</v>
       </c>
       <c r="H12" t="n">
-        <v>519.3438</v>
+        <v>519.34</v>
       </c>
     </row>
     <row r="13">
@@ -786,7 +786,7 @@
         <v>106.27</v>
       </c>
       <c r="H13" t="n">
-        <v>534.3919999999999</v>
+        <v>534.39</v>
       </c>
     </row>
     <row r="14">
@@ -814,7 +814,7 @@
         <v>106.44</v>
       </c>
       <c r="H14" t="n">
-        <v>525.479</v>
+        <v>525.48</v>
       </c>
     </row>
     <row r="15">

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -867,10 +867,10 @@
         <v>129.34</v>
       </c>
       <c r="G16" t="n">
-        <v>106.05</v>
+        <v>106.51</v>
       </c>
       <c r="H16" t="n">
-        <v>530.02</v>
+        <v>530.48</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,34 @@
         <v>530.48</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026年2月27日</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>127.62</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>127.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>134.64</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>127.62</v>
+        <v>262.26</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -889,7 +889,7 @@
         <v>127.62</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>171.82</v>
       </c>
       <c r="F17" t="n">
         <v>134.64</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>262.26</v>
+        <v>434.08</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -895,10 +895,10 @@
         <v>134.64</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>107.09</v>
       </c>
       <c r="H17" t="n">
-        <v>434.08</v>
+        <v>541.17</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -469,7 +469,7 @@
         <v>111.4</v>
       </c>
       <c r="E2" t="n">
-        <v>156.752</v>
+        <v>156.75</v>
       </c>
       <c r="F2" t="n">
         <v>114.38</v>
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>110.4577</v>
+        <v>110.45</v>
       </c>
       <c r="E5" t="n">
         <v>155.43</v>
@@ -562,7 +562,7 @@
         <v>103.54</v>
       </c>
       <c r="H5" t="n">
-        <v>482.03</v>
+        <v>482.02</v>
       </c>
     </row>
     <row r="6">
@@ -578,19 +578,19 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>111.1108</v>
+        <v>111.11</v>
       </c>
       <c r="E6" t="n">
         <v>154.99</v>
       </c>
       <c r="F6" t="n">
-        <v>113.2578</v>
+        <v>113.25</v>
       </c>
       <c r="G6" t="n">
         <v>103.54</v>
       </c>
       <c r="H6" t="n">
-        <v>482.9</v>
+        <v>482.89</v>
       </c>
     </row>
     <row r="7">
@@ -606,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>109.338</v>
+        <v>109.33</v>
       </c>
       <c r="E7" t="n">
         <v>154.32</v>
@@ -618,7 +618,7 @@
         <v>103.66</v>
       </c>
       <c r="H7" t="n">
-        <v>479.98</v>
+        <v>479.97</v>
       </c>
     </row>
     <row r="8">
@@ -640,7 +640,7 @@
         <v>154.16</v>
       </c>
       <c r="F8" t="n">
-        <v>113.635</v>
+        <v>113.63</v>
       </c>
       <c r="G8" t="n">
         <v>103.85</v>
@@ -662,7 +662,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>114.189</v>
+        <v>114.18</v>
       </c>
       <c r="E9" t="n">
         <v>160.25</v>
@@ -674,7 +674,7 @@
         <v>104.39</v>
       </c>
       <c r="H9" t="n">
-        <v>496.36</v>
+        <v>496.35</v>
       </c>
     </row>
     <row r="10">
@@ -696,7 +696,7 @@
         <v>159.28</v>
       </c>
       <c r="F10" t="n">
-        <v>117.2748</v>
+        <v>117.27</v>
       </c>
       <c r="G10" t="n">
         <v>104.05</v>
@@ -721,7 +721,7 @@
         <v>120.44</v>
       </c>
       <c r="E11" t="n">
-        <v>167.035</v>
+        <v>167.03</v>
       </c>
       <c r="F11" t="n">
         <v>123.63</v>
@@ -730,7 +730,7 @@
         <v>104.31</v>
       </c>
       <c r="H11" t="n">
-        <v>515.42</v>
+        <v>515.41</v>
       </c>
     </row>
     <row r="12">
@@ -749,16 +749,16 @@
         <v>120.25</v>
       </c>
       <c r="E12" t="n">
-        <v>167.3358</v>
+        <v>167.33</v>
       </c>
       <c r="F12" t="n">
-        <v>126.638</v>
+        <v>126.63</v>
       </c>
       <c r="G12" t="n">
         <v>105.12</v>
       </c>
       <c r="H12" t="n">
-        <v>519.34</v>
+        <v>519.33</v>
       </c>
     </row>
     <row r="13">
@@ -774,19 +774,19 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>125.477</v>
+        <v>125.47</v>
       </c>
       <c r="E13" t="n">
         <v>171.17</v>
       </c>
       <c r="F13" t="n">
-        <v>131.475</v>
+        <v>131.47</v>
       </c>
       <c r="G13" t="n">
         <v>106.27</v>
       </c>
       <c r="H13" t="n">
-        <v>534.39</v>
+        <v>534.38</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +802,7 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>122.679</v>
+        <v>122.67</v>
       </c>
       <c r="E14" t="n">
         <v>168.66</v>
@@ -814,7 +814,7 @@
         <v>106.44</v>
       </c>
       <c r="H14" t="n">
-        <v>525.48</v>
+        <v>525.47</v>
       </c>
     </row>
     <row r="15">

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,34 @@
         <v>541.17</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026年3月6日</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2417.19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2417.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -914,7 +914,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>2417.19</v>
+        <v>247.19</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2417.19</v>
+        <v>247.19</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>131.57</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>247.19</v>
+        <v>378.76</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -917,7 +917,7 @@
         <v>247.19</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>167.76</v>
       </c>
       <c r="F18" t="n">
         <v>131.57</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>378.76</v>
+        <v>546.52</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -923,10 +923,10 @@
         <v>131.57</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>107.04</v>
       </c>
       <c r="H18" t="n">
-        <v>546.52</v>
+        <v>653.5599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025年11月7日</t>
+          <t xml:space="preserve">2025年11月7日 </t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025年12月5日</t>
+          <t xml:space="preserve">2025年12月5日 </t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026年1月9日</t>
+          <t xml:space="preserve">2026年1月9日  </t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026年2月6日</t>
+          <t xml:space="preserve">2026年2月6日 </t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026年3月6日</t>
+          <t xml:space="preserve">2026年3月6日 </t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -927,6 +927,34 @@
       </c>
       <c r="H18" t="n">
         <v>653.5599999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026年3月13日</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17</v>
+      </c>
+      <c r="D19" t="n">
+        <v>243.14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>243.14</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -948,13 +948,13 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>130.74</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>243.14</v>
+        <v>373.88</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -945,16 +945,16 @@
         <v>243.14</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>166.92</v>
       </c>
       <c r="F19" t="n">
         <v>130.74</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>107.04</v>
       </c>
       <c r="H19" t="n">
-        <v>373.88</v>
+        <v>647.84</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -951,10 +951,10 @@
         <v>130.74</v>
       </c>
       <c r="G19" t="n">
-        <v>107.04</v>
+        <v>106.98</v>
       </c>
       <c r="H19" t="n">
-        <v>647.84</v>
+        <v>647.78</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,6 +957,34 @@
         <v>647.78</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026年3月20日</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="E20" t="n">
+        <v>158.92</v>
+      </c>
+      <c r="F20" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>106.98</v>
+      </c>
+      <c r="H20" t="n">
+        <v>628.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -976,13 +976,13 @@
         <v>158.92</v>
       </c>
       <c r="F20" t="n">
-        <v>123.9</v>
+        <v>123.95</v>
       </c>
       <c r="G20" t="n">
         <v>106.98</v>
       </c>
       <c r="H20" t="n">
-        <v>628.53</v>
+        <v>628.58</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -973,7 +973,7 @@
         <v>238.73</v>
       </c>
       <c r="E20" t="n">
-        <v>158.92</v>
+        <v>160.02</v>
       </c>
       <c r="F20" t="n">
         <v>123.95</v>
@@ -982,7 +982,7 @@
         <v>106.98</v>
       </c>
       <c r="H20" t="n">
-        <v>628.58</v>
+        <v>629.6799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -979,10 +979,10 @@
         <v>123.95</v>
       </c>
       <c r="G20" t="n">
-        <v>106.98</v>
+        <v>105.8</v>
       </c>
       <c r="H20" t="n">
-        <v>629.6799999999999</v>
+        <v>628.5</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,6 +985,34 @@
         <v>628.5</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026年3月27日</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="n">
+        <v>241.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>160</v>
+      </c>
+      <c r="F21" t="n">
+        <v>123</v>
+      </c>
+      <c r="G21" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>630.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -497,7 +497,7 @@
         <v>112.35</v>
       </c>
       <c r="E3" t="n">
-        <v>157.2</v>
+        <v>157.02</v>
       </c>
       <c r="F3" t="n">
         <v>115.52</v>
@@ -506,7 +506,7 @@
         <v>103.82</v>
       </c>
       <c r="H3" t="n">
-        <v>488.89</v>
+        <v>488.71</v>
       </c>
     </row>
     <row r="4">
@@ -1004,13 +1004,13 @@
         <v>160</v>
       </c>
       <c r="F21" t="n">
-        <v>123</v>
+        <v>123.93</v>
       </c>
       <c r="G21" t="n">
         <v>105.8</v>
       </c>
       <c r="H21" t="n">
-        <v>630.1</v>
+        <v>631.03</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1001,7 +1001,7 @@
         <v>241.3</v>
       </c>
       <c r="E21" t="n">
-        <v>160</v>
+        <v>160.3</v>
       </c>
       <c r="F21" t="n">
         <v>123.93</v>
@@ -1010,7 +1010,7 @@
         <v>105.8</v>
       </c>
       <c r="H21" t="n">
-        <v>631.03</v>
+        <v>631.33</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1007,10 +1007,10 @@
         <v>123.93</v>
       </c>
       <c r="G21" t="n">
-        <v>105.8</v>
+        <v>105.86</v>
       </c>
       <c r="H21" t="n">
-        <v>631.33</v>
+        <v>631.39</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,34 @@
         <v>631.39</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026年4月03日</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="E22" t="n">
+        <v>157.73</v>
+      </c>
+      <c r="F22" t="n">
+        <v>120.58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>105.86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>622.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1029,7 +1029,7 @@
         <v>238.73</v>
       </c>
       <c r="E22" t="n">
-        <v>157.73</v>
+        <v>157.7</v>
       </c>
       <c r="F22" t="n">
         <v>120.58</v>
@@ -1038,7 +1038,7 @@
         <v>105.86</v>
       </c>
       <c r="H22" t="n">
-        <v>622.9</v>
+        <v>622.87</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1032,13 +1032,13 @@
         <v>157.7</v>
       </c>
       <c r="F22" t="n">
-        <v>120.58</v>
+        <v>120.34</v>
       </c>
       <c r="G22" t="n">
         <v>105.86</v>
       </c>
       <c r="H22" t="n">
-        <v>622.87</v>
+        <v>622.63</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1035,10 +1035,10 @@
         <v>120.34</v>
       </c>
       <c r="G22" t="n">
-        <v>105.86</v>
+        <v>106.03</v>
       </c>
       <c r="H22" t="n">
-        <v>622.63</v>
+        <v>622.8</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1041,34 @@
         <v>622.8</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026年4月10日</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" t="n">
+        <v>244.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>157</v>
+      </c>
+      <c r="F23" t="n">
+        <v>120</v>
+      </c>
+      <c r="G23" t="n">
+        <v>106</v>
+      </c>
+      <c r="H23" t="n">
+        <v>627.0599999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1060,13 +1060,13 @@
         <v>157</v>
       </c>
       <c r="F23" t="n">
-        <v>120</v>
+        <v>128.51</v>
       </c>
       <c r="G23" t="n">
         <v>106</v>
       </c>
       <c r="H23" t="n">
-        <v>627.0599999999999</v>
+        <v>635.5700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1057,7 +1057,7 @@
         <v>244.06</v>
       </c>
       <c r="E23" t="n">
-        <v>157</v>
+        <v>168.2</v>
       </c>
       <c r="F23" t="n">
         <v>128.51</v>
@@ -1066,7 +1066,7 @@
         <v>106</v>
       </c>
       <c r="H23" t="n">
-        <v>635.5700000000001</v>
+        <v>646.77</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1063,10 +1063,10 @@
         <v>128.51</v>
       </c>
       <c r="G23" t="n">
-        <v>106</v>
+        <v>106.46</v>
       </c>
       <c r="H23" t="n">
-        <v>646.77</v>
+        <v>647.23</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,34 @@
         <v>647.23</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026年4月17日</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" t="n">
+        <v>249.59</v>
+      </c>
+      <c r="E24" t="n">
+        <v>168</v>
+      </c>
+      <c r="F24" t="n">
+        <v>128</v>
+      </c>
+      <c r="G24" t="n">
+        <v>106</v>
+      </c>
+      <c r="H24" t="n">
+        <v>651.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1088,13 +1088,13 @@
         <v>168</v>
       </c>
       <c r="F24" t="n">
-        <v>128</v>
+        <v>133.57</v>
       </c>
       <c r="G24" t="n">
         <v>106</v>
       </c>
       <c r="H24" t="n">
-        <v>651.59</v>
+        <v>657.16</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1085,7 +1085,7 @@
         <v>249.59</v>
       </c>
       <c r="E24" t="n">
-        <v>168</v>
+        <v>175.85</v>
       </c>
       <c r="F24" t="n">
         <v>133.57</v>
@@ -1094,7 +1094,7 @@
         <v>106</v>
       </c>
       <c r="H24" t="n">
-        <v>657.16</v>
+        <v>665.01</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1091,10 +1091,10 @@
         <v>133.57</v>
       </c>
       <c r="G24" t="n">
-        <v>106</v>
+        <v>106.83</v>
       </c>
       <c r="H24" t="n">
-        <v>665.01</v>
+        <v>665.84</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,34 @@
         <v>665.84</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026年4月24日</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" t="n">
+        <v>250.32</v>
+      </c>
+      <c r="E25" t="n">
+        <v>175</v>
+      </c>
+      <c r="F25" t="n">
+        <v>133</v>
+      </c>
+      <c r="G25" t="n">
+        <v>106</v>
+      </c>
+      <c r="H25" t="n">
+        <v>664.3200000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1116,13 +1116,13 @@
         <v>175</v>
       </c>
       <c r="F25" t="n">
-        <v>133</v>
+        <v>135.08</v>
       </c>
       <c r="G25" t="n">
         <v>106</v>
       </c>
       <c r="H25" t="n">
-        <v>664.3200000000001</v>
+        <v>666.4</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1113,7 +1113,7 @@
         <v>250.32</v>
       </c>
       <c r="E25" t="n">
-        <v>175</v>
+        <v>177.8</v>
       </c>
       <c r="F25" t="n">
         <v>135.08</v>
@@ -1122,7 +1122,7 @@
         <v>106</v>
       </c>
       <c r="H25" t="n">
-        <v>666.4</v>
+        <v>669.2</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1119,10 +1119,10 @@
         <v>135.08</v>
       </c>
       <c r="G25" t="n">
-        <v>106</v>
+        <v>106.71</v>
       </c>
       <c r="H25" t="n">
-        <v>669.2</v>
+        <v>669.91</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,34 @@
         <v>669.91</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026年4月30日</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>251.98</v>
+      </c>
+      <c r="E26" t="n">
+        <v>177</v>
+      </c>
+      <c r="F26" t="n">
+        <v>135</v>
+      </c>
+      <c r="G26" t="n">
+        <v>106</v>
+      </c>
+      <c r="H26" t="n">
+        <v>669.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1144,13 +1144,13 @@
         <v>177</v>
       </c>
       <c r="F26" t="n">
-        <v>135</v>
+        <v>137.1</v>
       </c>
       <c r="G26" t="n">
         <v>106</v>
       </c>
       <c r="H26" t="n">
-        <v>669.98</v>
+        <v>672.08</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1141,16 +1141,16 @@
         <v>251.98</v>
       </c>
       <c r="E26" t="n">
-        <v>177</v>
+        <v>179.9</v>
       </c>
       <c r="F26" t="n">
         <v>137.1</v>
       </c>
       <c r="G26" t="n">
-        <v>106</v>
+        <v>106.72</v>
       </c>
       <c r="H26" t="n">
-        <v>672.08</v>
+        <v>675.7</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,44 +429,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LQ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JHL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>GZ</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total_balance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +494,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -510,7 +522,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,7 +550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -566,7 +578,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -594,7 +606,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +662,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -678,7 +690,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -706,7 +718,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,7 +774,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -790,7 +802,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -818,7 +830,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -846,7 +858,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -902,7 +914,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -930,7 +942,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -958,7 +970,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -986,7 +998,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1014,7 +1026,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1042,7 +1054,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1070,7 +1082,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1126,7 +1138,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,44 +417,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>LQ</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JHL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GZ</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total_balance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,7 +482,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -522,7 +510,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,7 +538,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -578,7 +566,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -606,7 +594,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -662,7 +650,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -690,7 +678,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -718,7 +706,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -774,7 +762,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -802,7 +790,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,7 +818,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -858,7 +846,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -914,7 +902,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -942,7 +930,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -970,7 +958,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -998,7 +986,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1026,7 +1014,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1054,7 +1042,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1082,7 +1070,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1138,7 +1126,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1153,34 @@
         <v>675.7</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026年5月8日 </t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>261</v>
+      </c>
+      <c r="E27" t="n">
+        <v>180</v>
+      </c>
+      <c r="F27" t="n">
+        <v>140</v>
+      </c>
+      <c r="G27" t="n">
+        <v>106</v>
+      </c>
+      <c r="H27" t="n">
+        <v>687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1175,10 +1175,10 @@
         <v>140</v>
       </c>
       <c r="G27" t="n">
-        <v>106</v>
+        <v>106.89</v>
       </c>
       <c r="H27" t="n">
-        <v>687</v>
+        <v>687.89</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1166,19 +1166,19 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>261</v>
+        <v>261.01</v>
       </c>
       <c r="E27" t="n">
         <v>180</v>
       </c>
       <c r="F27" t="n">
-        <v>140</v>
+        <v>143.78</v>
       </c>
       <c r="G27" t="n">
         <v>106.89</v>
       </c>
       <c r="H27" t="n">
-        <v>687.89</v>
+        <v>691.6799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1169,7 +1169,7 @@
         <v>261.01</v>
       </c>
       <c r="E27" t="n">
-        <v>180</v>
+        <v>188.93</v>
       </c>
       <c r="F27" t="n">
         <v>143.78</v>
@@ -1178,7 +1178,7 @@
         <v>106.89</v>
       </c>
       <c r="H27" t="n">
-        <v>691.6799999999999</v>
+        <v>700.61</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1175,10 +1175,10 @@
         <v>143.78</v>
       </c>
       <c r="G27" t="n">
-        <v>106.89</v>
+        <v>107.07</v>
       </c>
       <c r="H27" t="n">
-        <v>700.61</v>
+        <v>700.79</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,6 +1181,34 @@
         <v>700.79</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026年5月15日</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" t="n">
+        <v>259.89</v>
+      </c>
+      <c r="E28" t="n">
+        <v>188</v>
+      </c>
+      <c r="F28" t="n">
+        <v>143</v>
+      </c>
+      <c r="G28" t="n">
+        <v>107</v>
+      </c>
+      <c r="H28" t="n">
+        <v>697.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1200,13 +1200,13 @@
         <v>188</v>
       </c>
       <c r="F28" t="n">
-        <v>143</v>
+        <v>144.63</v>
       </c>
       <c r="G28" t="n">
         <v>107</v>
       </c>
       <c r="H28" t="n">
-        <v>697.89</v>
+        <v>699.52</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1197,7 +1197,7 @@
         <v>259.89</v>
       </c>
       <c r="E28" t="n">
-        <v>188</v>
+        <v>187.9</v>
       </c>
       <c r="F28" t="n">
         <v>144.63</v>
@@ -1206,7 +1206,7 @@
         <v>107</v>
       </c>
       <c r="H28" t="n">
-        <v>699.52</v>
+        <v>699.42</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1203,10 +1203,10 @@
         <v>144.63</v>
       </c>
       <c r="G28" t="n">
-        <v>107</v>
+        <v>106.66</v>
       </c>
       <c r="H28" t="n">
-        <v>699.42</v>
+        <v>699.08</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1209,6 +1209,34 @@
         <v>699.08</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026年5月22日</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" t="n">
+        <v>262.1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>187</v>
+      </c>
+      <c r="F29" t="n">
+        <v>144</v>
+      </c>
+      <c r="G29" t="n">
+        <v>106</v>
+      </c>
+      <c r="H29" t="n">
+        <v>699.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1228,13 +1228,13 @@
         <v>187</v>
       </c>
       <c r="F29" t="n">
-        <v>144</v>
+        <v>148.65</v>
       </c>
       <c r="G29" t="n">
         <v>106</v>
       </c>
       <c r="H29" t="n">
-        <v>699.1</v>
+        <v>703.75</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1225,7 +1225,7 @@
         <v>262.1</v>
       </c>
       <c r="E29" t="n">
-        <v>187</v>
+        <v>188.12</v>
       </c>
       <c r="F29" t="n">
         <v>148.65</v>
@@ -1234,7 +1234,7 @@
         <v>106</v>
       </c>
       <c r="H29" t="n">
-        <v>703.75</v>
+        <v>704.87</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1231,10 +1231,10 @@
         <v>148.65</v>
       </c>
       <c r="G29" t="n">
-        <v>106</v>
+        <v>106.62</v>
       </c>
       <c r="H29" t="n">
-        <v>704.87</v>
+        <v>705.49</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1237,6 +1237,34 @@
         <v>705.49</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026年5月29日</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" t="n">
+        <v>255.66</v>
+      </c>
+      <c r="E30" t="n">
+        <v>188</v>
+      </c>
+      <c r="F30" t="n">
+        <v>148</v>
+      </c>
+      <c r="G30" t="n">
+        <v>106</v>
+      </c>
+      <c r="H30" t="n">
+        <v>697.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1256,13 +1256,13 @@
         <v>188</v>
       </c>
       <c r="F30" t="n">
-        <v>148</v>
+        <v>143.45</v>
       </c>
       <c r="G30" t="n">
         <v>106</v>
       </c>
       <c r="H30" t="n">
-        <v>697.66</v>
+        <v>693.11</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1253,16 +1253,16 @@
         <v>255.66</v>
       </c>
       <c r="E30" t="n">
-        <v>188</v>
+        <v>181.42</v>
       </c>
       <c r="F30" t="n">
         <v>143.45</v>
       </c>
       <c r="G30" t="n">
-        <v>106</v>
+        <v>106.25</v>
       </c>
       <c r="H30" t="n">
-        <v>693.11</v>
+        <v>686.78</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,34 @@
         <v>686.78</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026年6月 5日</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" t="n">
+        <v>253.45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>180</v>
+      </c>
+      <c r="F31" t="n">
+        <v>140</v>
+      </c>
+      <c r="G31" t="n">
+        <v>106</v>
+      </c>
+      <c r="H31" t="n">
+        <v>679.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1281,7 +1281,7 @@
         <v>253.45</v>
       </c>
       <c r="E31" t="n">
-        <v>180</v>
+        <v>182.07</v>
       </c>
       <c r="F31" t="n">
         <v>140</v>
@@ -1290,7 +1290,7 @@
         <v>106</v>
       </c>
       <c r="H31" t="n">
-        <v>679.45</v>
+        <v>681.52</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1284,13 +1284,13 @@
         <v>182.07</v>
       </c>
       <c r="F31" t="n">
-        <v>140</v>
+        <v>142.83</v>
       </c>
       <c r="G31" t="n">
         <v>106</v>
       </c>
       <c r="H31" t="n">
-        <v>681.52</v>
+        <v>684.35</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1287,10 +1287,10 @@
         <v>142.83</v>
       </c>
       <c r="G31" t="n">
-        <v>106</v>
+        <v>106.13</v>
       </c>
       <c r="H31" t="n">
-        <v>684.35</v>
+        <v>684.48</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,6 +1293,34 @@
         <v>684.48</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026年6月12日</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" t="n">
+        <v>244.98</v>
+      </c>
+      <c r="E32" t="n">
+        <v>180</v>
+      </c>
+      <c r="F32" t="n">
+        <v>140</v>
+      </c>
+      <c r="G32" t="n">
+        <v>106</v>
+      </c>
+      <c r="H32" t="n">
+        <v>670.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1312,13 +1312,13 @@
         <v>180</v>
       </c>
       <c r="F32" t="n">
-        <v>140</v>
+        <v>140.18</v>
       </c>
       <c r="G32" t="n">
         <v>106</v>
       </c>
       <c r="H32" t="n">
-        <v>670.98</v>
+        <v>671.16</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1309,7 +1309,7 @@
         <v>244.98</v>
       </c>
       <c r="E32" t="n">
-        <v>180</v>
+        <v>179.31</v>
       </c>
       <c r="F32" t="n">
         <v>140.18</v>
@@ -1318,7 +1318,7 @@
         <v>106</v>
       </c>
       <c r="H32" t="n">
-        <v>671.16</v>
+        <v>670.47</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1315,10 +1315,10 @@
         <v>140.18</v>
       </c>
       <c r="G32" t="n">
-        <v>106</v>
+        <v>105.65</v>
       </c>
       <c r="H32" t="n">
-        <v>670.47</v>
+        <v>670.12</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,6 +1321,34 @@
         <v>670.12</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026年6月19日</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D33" t="n">
+        <v>261.18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>180</v>
+      </c>
+      <c r="F33" t="n">
+        <v>140</v>
+      </c>
+      <c r="G33" t="n">
+        <v>105</v>
+      </c>
+      <c r="H33" t="n">
+        <v>686.1799999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1340,13 +1340,13 @@
         <v>180</v>
       </c>
       <c r="F33" t="n">
-        <v>140</v>
+        <v>149.19</v>
       </c>
       <c r="G33" t="n">
         <v>105</v>
       </c>
       <c r="H33" t="n">
-        <v>686.1799999999999</v>
+        <v>695.37</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1337,7 +1337,7 @@
         <v>261.18</v>
       </c>
       <c r="E33" t="n">
-        <v>180</v>
+        <v>192.17</v>
       </c>
       <c r="F33" t="n">
         <v>149.19</v>
@@ -1346,7 +1346,7 @@
         <v>105</v>
       </c>
       <c r="H33" t="n">
-        <v>695.37</v>
+        <v>707.54</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1343,10 +1343,10 @@
         <v>149.19</v>
       </c>
       <c r="G33" t="n">
-        <v>105</v>
+        <v>106.04</v>
       </c>
       <c r="H33" t="n">
-        <v>707.54</v>
+        <v>708.58</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +1349,34 @@
         <v>708.58</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026年6月26日</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" t="n">
+        <v>257.87</v>
+      </c>
+      <c r="E34" t="n">
+        <v>190</v>
+      </c>
+      <c r="F34" t="n">
+        <v>144.64</v>
+      </c>
+      <c r="G34" t="n">
+        <v>106</v>
+      </c>
+      <c r="H34" t="n">
+        <v>698.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1365,7 +1365,7 @@
         <v>257.87</v>
       </c>
       <c r="E34" t="n">
-        <v>190</v>
+        <v>187.98</v>
       </c>
       <c r="F34" t="n">
         <v>144.64</v>
@@ -1374,7 +1374,7 @@
         <v>106</v>
       </c>
       <c r="H34" t="n">
-        <v>698.51</v>
+        <v>696.49</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1371,10 +1371,10 @@
         <v>144.64</v>
       </c>
       <c r="G34" t="n">
-        <v>106</v>
+        <v>105.57</v>
       </c>
       <c r="H34" t="n">
-        <v>696.49</v>
+        <v>696.0599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,34 @@
         <v>696.0599999999999</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026年7月 3日</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>33</v>
+      </c>
+      <c r="D35" t="n">
+        <v>258.61</v>
+      </c>
+      <c r="E35" t="n">
+        <v>187</v>
+      </c>
+      <c r="F35" t="n">
+        <v>144</v>
+      </c>
+      <c r="G35" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" t="n">
+        <v>739.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1396,13 +1396,13 @@
         <v>187</v>
       </c>
       <c r="F35" t="n">
-        <v>144</v>
+        <v>146.95</v>
       </c>
       <c r="G35" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="H35" t="n">
-        <v>739.61</v>
+        <v>697.5599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1393,7 +1393,7 @@
         <v>258.61</v>
       </c>
       <c r="E35" t="n">
-        <v>187</v>
+        <v>193.28</v>
       </c>
       <c r="F35" t="n">
         <v>146.95</v>
@@ -1402,7 +1402,7 @@
         <v>105</v>
       </c>
       <c r="H35" t="n">
-        <v>697.5599999999999</v>
+        <v>703.84</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1399,10 +1399,10 @@
         <v>146.95</v>
       </c>
       <c r="G35" t="n">
-        <v>105</v>
+        <v>105.93</v>
       </c>
       <c r="H35" t="n">
-        <v>703.84</v>
+        <v>704.77</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,34 @@
         <v>704.77</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026年7月10日</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" t="n">
+        <v>248.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>290</v>
+      </c>
+      <c r="F36" t="n">
+        <v>140</v>
+      </c>
+      <c r="G36" t="n">
+        <v>105.93</v>
+      </c>
+      <c r="H36" t="n">
+        <v>784.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1421,16 +1421,16 @@
         <v>248.48</v>
       </c>
       <c r="E36" t="n">
-        <v>290</v>
+        <v>183.83</v>
       </c>
       <c r="F36" t="n">
-        <v>140</v>
+        <v>139.16</v>
       </c>
       <c r="G36" t="n">
         <v>105.93</v>
       </c>
       <c r="H36" t="n">
-        <v>784.41</v>
+        <v>677.4</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1421,7 +1421,7 @@
         <v>248.48</v>
       </c>
       <c r="E36" t="n">
-        <v>183.83</v>
+        <v>184.75</v>
       </c>
       <c r="F36" t="n">
         <v>139.16</v>
@@ -1430,7 +1430,7 @@
         <v>105.93</v>
       </c>
       <c r="H36" t="n">
-        <v>677.4</v>
+        <v>678.3200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1427,10 +1427,10 @@
         <v>139.16</v>
       </c>
       <c r="G36" t="n">
-        <v>105.93</v>
+        <v>105.45</v>
       </c>
       <c r="H36" t="n">
-        <v>678.3200000000001</v>
+        <v>677.84</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,6 +1433,62 @@
         <v>677.84</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026年7月17日</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="n">
+        <v>214.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>155.48</v>
+      </c>
+      <c r="F37" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="G37" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="H37" t="n">
+        <v>593.88</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026年7月24日</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" t="n">
+        <v>209.46</v>
+      </c>
+      <c r="E38" t="n">
+        <v>149.17</v>
+      </c>
+      <c r="F38" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="H38" t="n">
+        <v>577.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,6 +1489,34 @@
         <v>577.13</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026年8月14日</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" t="n">
+        <v>233.38</v>
+      </c>
+      <c r="E39" t="n">
+        <v>161.45</v>
+      </c>
+      <c r="F39" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" t="n">
+        <v>618.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1517,6 +1517,62 @@
         <v>618.61</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026年8月21日</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" t="n">
+        <v>231.36</v>
+      </c>
+      <c r="E40" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="F40" t="n">
+        <v>122</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="H40" t="n">
+        <v>611.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026年8月28日</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>158.81</v>
+      </c>
+      <c r="F41" t="n">
+        <v>124.29</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>618.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -1561,7 +1561,7 @@
         <v>235.6</v>
       </c>
       <c r="E41" t="n">
-        <v>158.81</v>
+        <v>158.71</v>
       </c>
       <c r="F41" t="n">
         <v>124.29</v>
@@ -1570,7 +1570,7 @@
         <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>618.7</v>
+        <v>618.6</v>
       </c>
     </row>
   </sheetData>

--- a/invest_output.xlsx
+++ b/invest_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1573,34 @@
         <v>618.6</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026年9月 4日</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>121.04</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>609.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
